--- a/artfynd/A 19602-2023 artfynd.xlsx
+++ b/artfynd/A 19602-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117477593</v>
       </c>
       <c r="B2" t="n">
-        <v>100117</v>
+        <v>100119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 19602-2023 artfynd.xlsx
+++ b/artfynd/A 19602-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>117477593</v>
       </c>
       <c r="B2" t="n">
-        <v>100119</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19602-2023 artfynd.xlsx
+++ b/artfynd/A 19602-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117477593</v>
       </c>
       <c r="B2" t="n">
-        <v>100933</v>
+        <v>100936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19602-2023 artfynd.xlsx
+++ b/artfynd/A 19602-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117477593</v>
       </c>
       <c r="B2" t="n">
-        <v>100936</v>
+        <v>100965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19602-2023 artfynd.xlsx
+++ b/artfynd/A 19602-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117477593</v>
       </c>
       <c r="B2" t="n">
-        <v>100965</v>
+        <v>100977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19602-2023 artfynd.xlsx
+++ b/artfynd/A 19602-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117477593</v>
       </c>
       <c r="B2" t="n">
-        <v>100977</v>
+        <v>100978</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19602-2023 artfynd.xlsx
+++ b/artfynd/A 19602-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117477593</v>
       </c>
       <c r="B2" t="n">
-        <v>100978</v>
+        <v>100983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19602-2023 artfynd.xlsx
+++ b/artfynd/A 19602-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117477593</v>
       </c>
       <c r="B2" t="n">
-        <v>100983</v>
+        <v>100987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19602-2023 artfynd.xlsx
+++ b/artfynd/A 19602-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117477593</v>
       </c>
       <c r="B2" t="n">
-        <v>100987</v>
+        <v>100989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19602-2023 artfynd.xlsx
+++ b/artfynd/A 19602-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117477593</v>
       </c>
       <c r="B2" t="n">
-        <v>100989</v>
+        <v>100999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19602-2023 artfynd.xlsx
+++ b/artfynd/A 19602-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117477593</v>
+        <v>6328146</v>
       </c>
       <c r="B2" t="n">
-        <v>100999</v>
+        <v>101348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -711,22 +711,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pålycke, 550 m NO Pålyckegölen, Bl</t>
+          <t>Pålycke, 300 m NO Pålyckegölen, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534341</v>
+        <v>534252</v>
       </c>
       <c r="R2" t="n">
-        <v>6237115</v>
+        <v>6236888</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +750,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>K-Kna-1166</t>
+          <t>K-Kna-1165</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2011-05-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2011-05-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ganska mycket avverkat kring lokalen. Väldigt torr mark.</t>
+          <t>vid skogsväg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,18 +777,154 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Öppen mark med buskar</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>vägslänt</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Åke Widgren</t>
+          <t>K-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åke Widgren</t>
+          <t>Kjell Pettersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6328147</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101348</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Pålycke, 550 m NO Pålyckegölen, Bl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>534341</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6237115</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fridlevstad</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>K-Kna-1166</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-05-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2011-05-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>vid skogsvägsvägskäl</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Öppen mark med buskar</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>K-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kjell Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 19602-2023 artfynd.xlsx
+++ b/artfynd/A 19602-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6328146</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -929,8 +939,17 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6328147</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>